--- a/outputs/hard_cheese/silpo_novus/primary_chain_output.xlsx
+++ b/outputs/hard_cheese/silpo_novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001649183941800067</v>
+        <v>0.001649183941799371</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1.66813437649029e-12</v>
+        <v>1.668134376491154e-12</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4.160589056408487e-21</v>
+        <v>4.160589056408666e-21</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.08893253878307611</v>
       </c>
       <c r="D3" t="n">
-        <v>1.532473806067052e-08</v>
+        <v>1.532473806066898e-08</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.196556730323243e-10</v>
+        <v>1.196556730322677e-10</v>
       </c>
       <c r="G3" t="n">
         <v>0.04166666666668085</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009639020091333781</v>
+        <v>0.009639020091333756</v>
       </c>
       <c r="C4" t="n">
         <v>0.1</v>
@@ -630,7 +630,7 @@
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001255316994740675</v>
+        <v>0.001255316994740617</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.2322700832601339</v>
+        <v>0.232270083260134</v>
       </c>
       <c r="N5" t="n">
         <v>189</v>
@@ -942,22 +942,22 @@
         <v>187</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.901684280673745</v>
+        <v>-1.901684280673758</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3195396559542991</v>
+        <v>0.3195396559542992</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.703887241265392</v>
+        <v>-0.7038872412653931</v>
       </c>
       <c r="M2" t="n">
-        <v>2.747609431022365e-15</v>
+        <v>2.747609431018937e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1625343111972001</v>
+        <v>0.1625343111971972</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2610022514748195</v>
+        <v>0.2610022514748128</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -1024,10 +1024,10 @@
         <v>49</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.331473746880862</v>
+        <v>-1.331473746880861</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.323240219425974</v>
+        <v>-3.323240219425985</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -1098,22 +1098,22 @@
         <v>47</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.286917649947797</v>
+        <v>-0.2869176499477997</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.00476787473343</v>
+        <v>-7.004767874733442</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5857286396943655</v>
+        <v>-0.5857286396943649</v>
       </c>
       <c r="M4" t="n">
-        <v>2.55590014871495e-09</v>
+        <v>2.555900148716638e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8452940711711397</v>
+        <v>0.8452940711711425</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0150142087144428</v>
+        <v>0.01501420871445145</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3045392670214256</v>
+        <v>0.3045392670214253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2688968463348229</v>
+        <v>0.2688968463348201</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05424410826903407</v>
+        <v>0.05424410826903467</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8676166313512811</v>
+        <v>0.8676166313512658</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4620989193669481</v>
+        <v>0.4620989193667864</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2508240957204422</v>
+        <v>0.2508240957205056</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9705702295552536</v>
+        <v>0.9705702295552534</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4964123783693583</v>
+        <v>0.4964123783693564</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1519817586058793</v>
+        <v>0.15198175860588</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -57325,10 +57325,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.852886918113318</v>
+        <v>-1.852886918113325</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04879736256042733</v>
+        <v>0.04879736256043321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57341,10 +57341,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.52011630994642</v>
+        <v>-1.520116309946426</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04003356383238164</v>
+        <v>0.04003356383238646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57357,10 +57357,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.579880495540932</v>
+        <v>-1.579880495540938</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04160750480205159</v>
+        <v>0.04160750480205661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57373,10 +57373,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.56914710204969</v>
+        <v>-1.569147102049695</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04132483169956718</v>
+        <v>0.04132483169957216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.571074773860019</v>
+        <v>-1.571074773860025</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04137559858625983</v>
+        <v>0.04137559858626482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57405,10 +57405,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.570728572203351</v>
+        <v>-1.570728572203357</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04136648106937615</v>
+        <v>0.04136648106938114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57421,10 +57421,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.57079074854812</v>
+        <v>-1.570790748548125</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04136811853662183</v>
+        <v>0.04136811853662681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57437,10 +57437,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.570779581941102</v>
+        <v>-1.570779581941108</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04136782445447042</v>
+        <v>0.04136782445447541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57453,10 +57453,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.570781587416219</v>
+        <v>-1.570781587416225</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04136787727037376</v>
+        <v>0.04136787727037875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57469,10 +57469,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.57078122724142</v>
+        <v>-1.570781227241425</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04136786778486221</v>
+        <v>0.04136786778486719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57485,10 +57485,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.570781291927281</v>
+        <v>-1.570781291927287</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04136786948841973</v>
+        <v>0.04136786948842472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57501,10 +57501,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.570781280309976</v>
+        <v>-1.570781280309981</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04136786918246804</v>
+        <v>0.04136786918247303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57517,10 +57517,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.570781282396394</v>
+        <v>-1.5707812823964</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04136786923741567</v>
+        <v>0.04136786923742065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57533,10 +57533,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.570781282021682</v>
+        <v>-1.570781282021688</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04136786922754731</v>
+        <v>0.04136786922755229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57549,10 +57549,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.570781282088979</v>
+        <v>-1.570781282088985</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04136786922931962</v>
+        <v>0.04136786922932461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57565,10 +57565,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.570781282076893</v>
+        <v>-1.570781282076898</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04136786922900132</v>
+        <v>0.04136786922900631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57581,10 +57581,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.570781282079064</v>
+        <v>-1.570781282079069</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04136786922905849</v>
+        <v>0.04136786922906347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57597,10 +57597,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.570781282078674</v>
+        <v>-1.570781282078679</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04136786922904822</v>
+        <v>0.04136786922905321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57613,10 +57613,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.570781282078744</v>
+        <v>-1.570781282078749</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04136786922905007</v>
+        <v>0.04136786922905505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57629,10 +57629,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.570781282078731</v>
+        <v>-1.570781282078737</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04136786922904973</v>
+        <v>0.04136786922905472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57645,10 +57645,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.570781282078733</v>
+        <v>-1.570781282078739</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04136786922904979</v>
+        <v>0.04136786922905478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -57661,10 +57661,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>1.564951542122924</v>
+        <v>1.56495154212292</v>
       </c>
       <c r="C23" t="n">
-        <v>1.851869192070721</v>
+        <v>1.85186919207072</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -57677,10 +57677,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>1.025540796532843</v>
+        <v>1.02554079653284</v>
       </c>
       <c r="C24" t="n">
-        <v>1.213563075400109</v>
+        <v>1.213563075400108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -57693,10 +57693,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>1.211466011867844</v>
+        <v>1.211466011867841</v>
       </c>
       <c r="C25" t="n">
-        <v>1.433575752496126</v>
+        <v>1.433575752496125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -57709,10 +57709,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>1.147380922759077</v>
+        <v>1.147380922759075</v>
       </c>
       <c r="C26" t="n">
-        <v>1.357741326319171</v>
+        <v>1.35774132631917</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -57725,10 +57725,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>1.169469904281453</v>
+        <v>1.16946990428145</v>
       </c>
       <c r="C27" t="n">
-        <v>1.383880093727916</v>
+        <v>1.383880093727915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -57741,10 +57741,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>1.161856228284721</v>
+        <v>1.161856228284718</v>
       </c>
       <c r="C28" t="n">
-        <v>1.374870529126554</v>
+        <v>1.374870529126553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>1.164480525929431</v>
+        <v>1.164480525929428</v>
       </c>
       <c r="C29" t="n">
         <v>1.377975964552669</v>
@@ -57773,10 +57773,10 @@
         <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>1.163575977570532</v>
+        <v>1.163575977570529</v>
       </c>
       <c r="C30" t="n">
-        <v>1.376905576624676</v>
+        <v>1.376905576624675</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -57789,10 +57789,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>1.163887759176264</v>
+        <v>1.163887759176262</v>
       </c>
       <c r="C31" t="n">
-        <v>1.377274520157283</v>
+        <v>1.377274520157282</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -57805,10 +57805,10 @@
         <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>1.163780293645299</v>
+        <v>1.163780293645296</v>
       </c>
       <c r="C32" t="n">
-        <v>1.377147351934723</v>
+        <v>1.377147351934722</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>1.163817335087556</v>
+        <v>1.163817335087554</v>
       </c>
       <c r="C33" t="n">
         <v>1.377191184541612</v>
@@ -57837,7 +57837,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>1.16380456756636</v>
+        <v>1.163804567566357</v>
       </c>
       <c r="C34" t="n">
         <v>1.377176076227695</v>
@@ -57853,10 +57853,10 @@
         <v>12</v>
       </c>
       <c r="B35" t="n">
-        <v>1.163808968302065</v>
+        <v>1.163808968302062</v>
       </c>
       <c r="C35" t="n">
-        <v>1.377181283792694</v>
+        <v>1.377181283792693</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -57869,10 +57869,10 @@
         <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>1.163807451447348</v>
+        <v>1.163807451447346</v>
       </c>
       <c r="C36" t="n">
-        <v>1.377179488838382</v>
+        <v>1.377179488838381</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>1.16380797427998</v>
+        <v>1.163807974279977</v>
       </c>
       <c r="C37" t="n">
         <v>1.377180107526959</v>
@@ -57901,7 +57901,7 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>1.163807794068944</v>
+        <v>1.163807794068941</v>
       </c>
       <c r="C38" t="n">
         <v>1.377179894276096</v>
@@ -57917,7 +57917,7 @@
         <v>16</v>
       </c>
       <c r="B39" t="n">
-        <v>1.163807856184458</v>
+        <v>1.163807856184455</v>
       </c>
       <c r="C39" t="n">
         <v>1.377179967779846</v>
@@ -57933,10 +57933,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="n">
-        <v>1.163807834774353</v>
+        <v>1.163807834774351</v>
       </c>
       <c r="C40" t="n">
-        <v>1.377179942444421</v>
+        <v>1.37717994244442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -57949,10 +57949,10 @@
         <v>18</v>
       </c>
       <c r="B41" t="n">
-        <v>1.163807842154033</v>
+        <v>1.16380784215403</v>
       </c>
       <c r="C41" t="n">
-        <v>1.377179951177088</v>
+        <v>1.377179951177087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -57965,10 +57965,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="n">
-        <v>1.163807839610389</v>
+        <v>1.163807839610387</v>
       </c>
       <c r="C42" t="n">
-        <v>1.377179948167095</v>
+        <v>1.377179948167094</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -57981,10 +57981,10 @@
         <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>1.163807840487137</v>
+        <v>1.163807840487135</v>
       </c>
       <c r="C43" t="n">
-        <v>1.377179949204585</v>
+        <v>1.377179949204584</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
